--- a/data/2026-10/flujo_licitaciones_2026-10-06.xlsx
+++ b/data/2026-10/flujo_licitaciones_2026-10-06.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⏳ Licitaciones Abiertas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="✅ Adjudicados con CUIT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🔗 Flujo Cruzado" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⏳ Licitaciones Abiertas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,6 +415,414 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha_extraccion</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>fecha_publicacion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>organismo_contratante</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>tipo_proceso</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>aviso_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>proveedor_adjudicado</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>cuit_proveedor</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>monto_adjudicado</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>texto_muestra</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA CUYO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Licitación Pública 04/25</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2418644</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418644/20261006</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>SEPULVEDA EDUARDO</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>20240385474</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>$161.000.795,88</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/pdf/linkQR/NDdzV016NU9tVUpSbkVWUVVZR3c4dz09
+AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO -
+DIRECCIÓN REGIONAL ADUANERA CUYO
+Licitación Pública 04/25
+PRORROGA  LICITACIÓN  PÚBLICA  04/25  DI  RACU  Expediente  Nº:  EX-2025-03067525-  -ARCA-
+SECFDVAFCU#SDGOAI Objeto d</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>BORA Adjudicaciones</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>organismo_contratante</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tipo_proceso_bora</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>link_bora</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>proveedor_adjudicado</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>cuit_proveedor</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>monto_adjudicado_bora</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>en_comprar</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>procesos_comprar</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>unidad_comprar</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>nro_proceso_comprar</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>cobro_en_tgn</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>beneficiario_tgn</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>monto_cobrado_tgn</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>metodo_cruce_tgn</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>etapa</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>indicadores_riesgo</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>score_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>indice_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>nivel_riesgo_licit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MINISTERIO PÚBLICO DE LA DEFENSA - DEFENSORÍA GENERAL DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Licitación Pública 54/2025</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418643/20261006</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ARMANDO JOSE CUDINI – Autorización de venta INMOBILIARIA GABRIELA DI ORIO</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>⚠️ SIN CUIT EXTRAÍDO</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA CUYO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Licitación Pública 04/25</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418644/20261006</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SEPULVEDA EDUARDO</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>20240385474</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>$161.000.795,88</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>✅ ADJUDICADO (sin pago aún)</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
